--- a/HCVData/subtyping-comparison/11-report-subtype-agreement/NS5B_CometFullSeqSubtype_3B_Subtyping_Distances.xlsx
+++ b/HCVData/subtyping-comparison/11-report-subtype-agreement/NS5B_CometFullSeqSubtype_3B_Subtyping_Distances.xlsx
@@ -431,65 +431,70 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Genotype1Distance</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Genotype2Distance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Genotype3Distance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Genotype4Distance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Genotype5Distance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Genotype6Distance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Genotype7Distance</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Genotype8Distance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>FirstChoiceGenotype</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>SecondChoiceGenotype</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -503,60 +508,65 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>377</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>30.504</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>33.158</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>31.217</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>32.895</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>31.481</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>25.266</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>33.421</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>25.266</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>30.504</t>
         </is>
@@ -570,65 +580,70 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>659</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>27.753</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>32.188</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>17.299</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>29.091</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>29.714</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>31.259</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>30.971</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>28.484</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>17.299</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>27.753</t>
         </is>
@@ -642,65 +657,70 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>329</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>27.356</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>29.758</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>21.713</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>28.395</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>32.110</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>30.537</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>28.829</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>28.881</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>21.713</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>27.356</t>
         </is>
@@ -714,45 +734,50 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>24.561</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>23.664</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>30.592</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>32.107</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>24.561</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>30.592</t>
         </is>
@@ -766,45 +791,50 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>300</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>24.242</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>23.664</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>28.293</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>33.071</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>24.242</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>28.293</t>
         </is>
@@ -818,55 +848,60 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>29.970</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>31.868</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>23.030</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>28.614</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>32.923</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>30.303</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>23.030</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>28.614</t>
         </is>
@@ -880,65 +915,70 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>321</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>29.814</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>32.967</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>22.590</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>27.476</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>27.933</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>34.082</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>32.014</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>26.978</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>22.590</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>27.476</t>
         </is>
@@ -952,45 +992,50 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>28.448</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>33.659</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>20.727</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>27.488</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>20.727</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>27.488</t>
         </is>
@@ -1017,150 +1062,155 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype1aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype1aDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Subtype1bDistance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Subtype1bDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Subtype1cDistance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Subtype1cDistance</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Subtype1dDistance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Subtype1eDistance</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Subtype1eDistance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Subtype1gDistance</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Subtype1gDistance</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Subtype1hDistance</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Subtype1hDistance</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Subtype1iDistance</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Subtype1jDistance</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Subtype1kDistance</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Subtype1lDistance</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Subtype1lDistance</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Subtype1mDistance</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Subtype1mDistance</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Subtype1nDistance</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Subtype1nDistance</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Subtype1oDistance</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Subtype1oDistance</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -1187,145 +1237,150 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype2aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype2aDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Subtype2bDistance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Subtype2bDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Subtype2cDistance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Subtype2dDistance</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Subtype2eDistance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Subtype2fDistance</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Subtype2fDistance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Subtype2iDistance</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Subtype2jDistance</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Subtype2jDistance</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Subtype2kDistance</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Subtype2lDistance</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Subtype2lDistance</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Subtype2mDistance</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Subtype2mDistance</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Subtype2qDistance</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Subtype2qDistance</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Subtype2rDistance</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Subtype2tDistance</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Subtype2uDistance</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Subtype2vDistance</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -1352,85 +1407,90 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype3aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype3bDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Subtype3dDistance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Subtype3eDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Subtype3gDistance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Subtype3gDistance</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Subtype3hDistance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Subtype3iDistance</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Subtype3iDistance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Subtype3kDistance</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Subtype3kDistance</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -1444,85 +1504,90 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>659</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>19.272</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>7.891</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>18.361</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>21.851</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>15.175</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>15.175</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>25.797</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>18.058</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>18.058</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>23.449</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>23.449</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>3b</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>7.891</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>15.175</t>
         </is>
@@ -1536,85 +1601,90 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>329</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>22.018</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>19.572</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>25.076</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>24.924</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>18.541</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>18.541</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>23.913</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>21.407</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>21.407</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>26.606</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>26.606</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>18.541</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>3b</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>19.572</t>
         </is>
@@ -1628,80 +1698,85 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>26.364</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>29.333</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>26.901</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>28.657</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>30.547</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>30.547</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>27.796</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>27.796</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>31.169</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>31.169</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>3a</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>26.364</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>3d</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>26.901</t>
         </is>
@@ -1715,80 +1790,85 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>300</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>26.000</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>26.866</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>27.397</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>27.740</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>30.690</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>30.690</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>28.179</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>28.179</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>25.954</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>25.954</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>3a</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>26.000</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>3d</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>27.397</t>
         </is>
@@ -1802,85 +1882,90 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>23.636</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>10.542</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>24.085</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>22.866</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>16.364</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>16.364</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>24.383</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>20.303</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>20.303</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>23.826</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>23.826</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>3b</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>10.542</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>16.364</t>
         </is>
@@ -1894,85 +1979,90 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>321</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>20.872</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>9.034</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>23.810</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>24.702</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>15.888</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>15.888</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>21.754</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>18.438</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>18.438</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>20.956</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>20.956</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>3b</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>9.034</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>15.888</t>
         </is>
@@ -1986,85 +2076,90 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>21.612</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>7.527</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>19.424</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>21.455</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>15.884</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>15.884</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>24.000</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>20.364</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>20.364</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>23.188</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>23.188</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>3b</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>7.527</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>15.884</t>
         </is>
@@ -2091,145 +2186,150 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype4aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype4bDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Subtype4cDistance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Subtype4dDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Subtype4dDistance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Subtype4fDistance</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Subtype4fDistance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Subtype4gDistance</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Subtype4kDistance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Subtype4kDistance</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Subtype4lDistance</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Subtype4mDistance</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Subtype4nDistance</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Subtype4oDistance</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Subtype4pDistance</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Subtype4qDistance</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Subtype4rDistance</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Subtype4sDistance</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Subtype4tDistance</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Subtype4vDistance</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Subtype4vDistance</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Subtype4wDistance</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Subtype4wDistance</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -2256,40 +2356,45 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype5aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype5bDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -2316,255 +2421,260 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype6aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype6aDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Subtype6bDistance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Subtype6cDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Subtype6dDistance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Subtype6eDistance</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Subtype6fDistance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Subtype6gDistance</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Subtype6hDistance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Subtype6iDistance</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Subtype6jDistance</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Subtype6kDistance</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Subtype6lDistance</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Subtype6mDistance</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Subtype6nDistance</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Subtype6nDistance</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Subtype6oDistance</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Subtype6pDistance</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Subtype6qDistance</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Subtype6rDistance</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Subtype6sDistance</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Subtype6tDistance</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Subtype6tDistance</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Subtype6uDistance</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Subtype6vDistance</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Subtype6vDistance</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Subtype6wDistance</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Subtype6wDistance</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Subtype6xaDistance</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Subtype6xaDistance</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Subtype6xbDistance</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Subtype6xbDistance</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Subtype6xcDistance</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Subtype6xdDistance</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Subtype6xdDistance</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Subtype6xeDistance</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Subtype6xeDistance</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Subtype6xfDistance</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Subtype6xfDistance</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Subtype6xgDistance</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Subtype6xgDistance</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Subtype6xhDistance</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Subtype6xiDistance</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Subtype6xiDistance</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Subtype6xjDistance</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -2578,255 +2688,260 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>377</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>25.397</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>25.397</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>25.266</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>25.661</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>25.464</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>24.011</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>25.263</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>27.321</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>28.382</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>28.042</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>28.496</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>27.297</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>26.455</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>26.984</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>24.868</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>24.868</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>26.720</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>25.132</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>27.249</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>25.995</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>29.443</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>27.249</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>27.249</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>22.487</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>27.586</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>27.586</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>25.858</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>25.858</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>22.812</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>22.812</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>27.249</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>27.249</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>25.464</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>25.926</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>25.926</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>27.249</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>27.249</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>26.053</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>26.053</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>25.661</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>25.661</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>26.260</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>25.661</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>25.661</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>28.871</t>
         </is>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>6xa</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>22.812</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>6u</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>22.487</t>
         </is>
@@ -2853,40 +2968,45 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype7aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype7bDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -2913,35 +3033,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype8aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
